--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76340763-E310-4A27-90EB-0FAA816A1722}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702F08C4-EED9-47A1-B0A2-58CE9C4A238A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>A股代码</t>
   </si>
@@ -108,6 +108,12 @@
   <si>
     <t>中矿资源</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>601088</t>
+  </si>
+  <si>
+    <t>中国神华</t>
   </si>
 </sst>
 </file>
@@ -156,10 +162,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -440,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC382BE-E169-4E26-B350-7F11F43F3F9C}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -459,50 +466,50 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -527,6 +534,22 @@
       </c>
       <c r="B10" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702F08C4-EED9-47A1-B0A2-58CE9C4A238A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464894BA-D796-4D68-8D66-228C978BF27A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>A股代码</t>
   </si>
@@ -66,10 +66,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>buydate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>002466</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -114,6 +110,9 @@
   </si>
   <si>
     <t>中国神华</t>
+  </si>
+  <si>
+    <t>长江电力</t>
   </si>
 </sst>
 </file>
@@ -447,24 +446,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC382BE-E169-4E26-B350-7F11F43F3F9C}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -472,7 +468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -480,15 +476,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -496,7 +492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -504,53 +500,57 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>600900</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464894BA-D796-4D68-8D66-228C978BF27A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4163D55F-356D-46DB-B27B-53F45DB56172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,7 +541,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>600900</v>
       </c>
       <c r="B12" s="3" t="s">

--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4163D55F-356D-46DB-B27B-53F45DB56172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472A6602-3D67-48D2-ABC6-6F2BF34DC7F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>A股代码</t>
   </si>
@@ -113,6 +113,14 @@
   </si>
   <si>
     <t>长江电力</t>
+  </si>
+  <si>
+    <t>600519</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵州茅台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -462,10 +470,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -478,18 +486,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,56 +509,60 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
+      <c r="A11" s="2">
+        <v>600900</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>600900</v>
+      <c r="A12" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472A6602-3D67-48D2-ABC6-6F2BF34DC7F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA27CFDC-59C7-44BC-913E-DA513E6761CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/input/selectlist_my.xlsx
+++ b/input/selectlist_my.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA27CFDC-59C7-44BC-913E-DA513E6761CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BAB447-6652-4677-8E91-177727EFAC3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>A股代码</t>
   </si>
@@ -120,6 +120,10 @@
   </si>
   <si>
     <t>贵州茅台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>健帆生物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC382BE-E169-4E26-B350-7F11F43F3F9C}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -564,6 +568,14 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>300529</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
